--- a/api/templates/export/supplies/en.xlsx
+++ b/api/templates/export/supplies/en.xlsx
@@ -227,57 +227,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -353,16 +308,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -371,7 +323,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -783,18 +738,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.5" style="4" customWidth="1"/>
     <col min="2" max="2" width="31.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="22" style="2" customWidth="1"/>
     <col min="4" max="4" width="21.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="19.375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>41</v>
       </c>
     </row>
@@ -802,27 +757,36 @@
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:5" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="10" t="s">
         <v>45</v>
       </c>
     </row>
@@ -830,148 +794,18 @@
       <c r="A6" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
